--- a/Customer_Sales_Report_Karen.xlsx
+++ b/Customer_Sales_Report_Karen.xlsx
@@ -2175,7 +2175,7 @@
         <v>59403014.27</v>
       </c>
       <c r="D2" t="n">
-        <v>5854783.96</v>
+        <v>6791549.393599999</v>
       </c>
       <c r="E2" t="n">
         <v>8.971776735961752</v>
@@ -2194,7 +2194,7 @@
         <v>24027540.97</v>
       </c>
       <c r="D3" t="n">
-        <v>2053499.93</v>
+        <v>2382059.9188</v>
       </c>
       <c r="E3" t="n">
         <v>7.87353517780803</v>
@@ -2213,7 +2213,7 @@
         <v>11973368.07</v>
       </c>
       <c r="D4" t="n">
-        <v>826399.97</v>
+        <v>958623.9651999999</v>
       </c>
       <c r="E4" t="n">
         <v>6.456366767096508</v>
@@ -2232,7 +2232,7 @@
         <v>9660317.890000001</v>
       </c>
       <c r="D5" t="n">
-        <v>667983.8199999999</v>
+        <v>774861.2311999999</v>
       </c>
       <c r="E5" t="n">
         <v>6.467508780782895</v>
@@ -2251,7 +2251,7 @@
         <v>8779017.42</v>
       </c>
       <c r="D6" t="n">
-        <v>804982.49</v>
+        <v>933779.6883999999</v>
       </c>
       <c r="E6" t="n">
         <v>8.399233071361746</v>
@@ -2270,7 +2270,7 @@
         <v>8017048.96</v>
       </c>
       <c r="D7" t="n">
-        <v>668058.74</v>
+        <v>774948.1383999999</v>
       </c>
       <c r="E7" t="n">
         <v>7.692002944304306</v>
@@ -2289,7 +2289,7 @@
         <v>5212900.02</v>
       </c>
       <c r="D8" t="n">
-        <v>207237.91</v>
+        <v>240395.9756</v>
       </c>
       <c r="E8" t="n">
         <v>3.823480374050186</v>
@@ -2308,7 +2308,7 @@
         <v>3137130.33</v>
       </c>
       <c r="D9" t="n">
-        <v>187938.63</v>
+        <v>218008.8108</v>
       </c>
       <c r="E9" t="n">
         <v>5.65217239885455</v>
@@ -2327,7 +2327,7 @@
         <v>2721701.94</v>
       </c>
       <c r="D10" t="n">
-        <v>278453.32</v>
+        <v>323005.8512</v>
       </c>
       <c r="E10" t="n">
         <v>9.281296995276172</v>
@@ -2346,7 +2346,7 @@
         <v>2805403.4</v>
       </c>
       <c r="D11" t="n">
-        <v>135372.43</v>
+        <v>157032.0188</v>
       </c>
       <c r="E11" t="n">
         <v>4.603289669991609</v>
@@ -2365,7 +2365,7 @@
         <v>2602242.1</v>
       </c>
       <c r="D12" t="n">
-        <v>182132.83</v>
+        <v>211274.0828</v>
       </c>
       <c r="E12" t="n">
         <v>6.541246584201933</v>
@@ -2384,7 +2384,7 @@
         <v>2552754.59</v>
       </c>
       <c r="D13" t="n">
-        <v>157676.45</v>
+        <v>182904.682</v>
       </c>
       <c r="E13" t="n">
         <v>5.81739390056572</v>
@@ -2403,7 +2403,7 @@
         <v>2436464.5</v>
       </c>
       <c r="D14" t="n">
-        <v>161156.14</v>
+        <v>186941.1224</v>
       </c>
       <c r="E14" t="n">
         <v>6.203990587324561</v>
@@ -2422,7 +2422,7 @@
         <v>2444819.91</v>
       </c>
       <c r="D15" t="n">
-        <v>103356.82</v>
+        <v>119893.9112</v>
       </c>
       <c r="E15" t="n">
         <v>4.056108777039181</v>
@@ -2441,7 +2441,7 @@
         <v>2105159.14</v>
       </c>
       <c r="D16" t="n">
-        <v>157888.27</v>
+        <v>183150.3932</v>
       </c>
       <c r="E16" t="n">
         <v>6.976799041077092</v>
@@ -2460,7 +2460,7 @@
         <v>2143940.99</v>
       </c>
       <c r="D17" t="n">
-        <v>77188.34</v>
+        <v>89538.47439999999</v>
       </c>
       <c r="E17" t="n">
         <v>3.475184400901139</v>
@@ -2479,7 +2479,7 @@
         <v>1875473.28</v>
       </c>
       <c r="D18" t="n">
-        <v>204552.55</v>
+        <v>237280.958</v>
       </c>
       <c r="E18" t="n">
         <v>9.834135088601279</v>
@@ -2498,7 +2498,7 @@
         <v>1843790.54</v>
       </c>
       <c r="D19" t="n">
-        <v>111093.06</v>
+        <v>128867.9496</v>
       </c>
       <c r="E19" t="n">
         <v>5.682847817639884</v>
@@ -2517,7 +2517,7 @@
         <v>1885728.85</v>
       </c>
       <c r="D20" t="n">
-        <v>59064.27</v>
+        <v>68514.55319999999</v>
       </c>
       <c r="E20" t="n">
         <v>3.037046428876712</v>
@@ -2536,7 +2536,7 @@
         <v>1821557.67</v>
       </c>
       <c r="D21" t="n">
-        <v>86056.11</v>
+        <v>99825.0876</v>
       </c>
       <c r="E21" t="n">
         <v>4.511191463504735</v>
@@ -2555,7 +2555,7 @@
         <v>1596546.75</v>
       </c>
       <c r="D22" t="n">
-        <v>173035.06</v>
+        <v>200720.6696</v>
       </c>
       <c r="E22" t="n">
         <v>9.778302366252284</v>
@@ -2574,7 +2574,7 @@
         <v>1535431.11</v>
       </c>
       <c r="D23" t="n">
-        <v>157245.6</v>
+        <v>182404.896</v>
       </c>
       <c r="E23" t="n">
         <v>9.289759767534109</v>
@@ -2593,7 +2593,7 @@
         <v>1441274.59</v>
       </c>
       <c r="D24" t="n">
-        <v>79156.42999999999</v>
+        <v>91821.45879999998</v>
       </c>
       <c r="E24" t="n">
         <v>5.206183572866068</v>
@@ -2612,7 +2612,7 @@
         <v>1231447.26</v>
       </c>
       <c r="D25" t="n">
-        <v>92539.74000000001</v>
+        <v>107346.0984</v>
       </c>
       <c r="E25" t="n">
         <v>6.989474919395169</v>
@@ -2631,7 +2631,7 @@
         <v>1154105.01</v>
       </c>
       <c r="D26" t="n">
-        <v>150860.53</v>
+        <v>174998.2148</v>
       </c>
       <c r="E26" t="n">
         <v>11.560499137778</v>
@@ -2650,7 +2650,7 @@
         <v>1196147.3</v>
       </c>
       <c r="D27" t="n">
-        <v>105611.35</v>
+        <v>122509.166</v>
       </c>
       <c r="E27" t="n">
         <v>8.112974705411023</v>
@@ -2669,7 +2669,7 @@
         <v>1015661.12</v>
       </c>
       <c r="D28" t="n">
-        <v>75131.97</v>
+        <v>87153.0852</v>
       </c>
       <c r="E28" t="n">
         <v>6.887829661627211</v>
@@ -2688,7 +2688,7 @@
         <v>1008746.64</v>
       </c>
       <c r="D29" t="n">
-        <v>57231.8</v>
+        <v>66388.88799999999</v>
       </c>
       <c r="E29" t="n">
         <v>5.368945360658514</v>
@@ -2707,7 +2707,7 @@
         <v>952942.54</v>
       </c>
       <c r="D30" t="n">
-        <v>85867.78999999999</v>
+        <v>99606.63639999999</v>
       </c>
       <c r="E30" t="n">
         <v>8.265973827965304</v>
@@ -2726,7 +2726,7 @@
         <v>994353.16</v>
       </c>
       <c r="D31" t="n">
-        <v>21987.35</v>
+        <v>25505.326</v>
       </c>
       <c r="E31" t="n">
         <v>2.163384198864611</v>
@@ -2745,7 +2745,7 @@
         <v>913767.96</v>
       </c>
       <c r="D32" t="n">
-        <v>39167.36</v>
+        <v>45434.13759999999</v>
       </c>
       <c r="E32" t="n">
         <v>4.110180321577334</v>
@@ -2764,7 +2764,7 @@
         <v>897067.2</v>
       </c>
       <c r="D33" t="n">
-        <v>44743.16</v>
+        <v>51902.0656</v>
       </c>
       <c r="E33" t="n">
         <v>4.750761076784078</v>
@@ -2783,7 +2783,7 @@
         <v>844974.02</v>
       </c>
       <c r="D34" t="n">
-        <v>54181.14</v>
+        <v>62850.12239999999</v>
       </c>
       <c r="E34" t="n">
         <v>6.02578313624981</v>
@@ -2802,7 +2802,7 @@
         <v>762970.01</v>
       </c>
       <c r="D35" t="n">
-        <v>47310.18</v>
+        <v>54879.8088</v>
       </c>
       <c r="E35" t="n">
         <v>5.838743262376933</v>
@@ -2821,7 +2821,7 @@
         <v>674020.62</v>
       </c>
       <c r="D36" t="n">
-        <v>127543.89</v>
+        <v>147950.9124</v>
       </c>
       <c r="E36" t="n">
         <v>15.91186840345514</v>
@@ -2840,7 +2840,7 @@
         <v>756818</v>
       </c>
       <c r="D37" t="n">
-        <v>27664.74</v>
+        <v>32091.0984</v>
       </c>
       <c r="E37" t="n">
         <v>3.526494413376132</v>
@@ -2859,7 +2859,7 @@
         <v>740183.7</v>
       </c>
       <c r="D38" t="n">
-        <v>40462.85</v>
+        <v>46936.906</v>
       </c>
       <c r="E38" t="n">
         <v>5.183248424014683</v>
@@ -2878,7 +2878,7 @@
         <v>644861.3199999999</v>
       </c>
       <c r="D39" t="n">
-        <v>37854.2</v>
+        <v>43910.872</v>
       </c>
       <c r="E39" t="n">
         <v>5.544652038963461</v>
@@ -2897,7 +2897,7 @@
         <v>488668.44</v>
       </c>
       <c r="D40" t="n">
-        <v>65547.02</v>
+        <v>76034.5432</v>
       </c>
       <c r="E40" t="n">
         <v>11.8269923397662</v>
@@ -2916,7 +2916,7 @@
         <v>525722.16</v>
       </c>
       <c r="D41" t="n">
-        <v>25251.97</v>
+        <v>29292.2852</v>
       </c>
       <c r="E41" t="n">
         <v>4.583149847707007</v>
@@ -2935,7 +2935,7 @@
         <v>503595.03</v>
       </c>
       <c r="D42" t="n">
-        <v>32094.62</v>
+        <v>37229.75919999999</v>
       </c>
       <c r="E42" t="n">
         <v>5.991271251927305</v>
@@ -2954,7 +2954,7 @@
         <v>443890.7</v>
       </c>
       <c r="D43" t="n">
-        <v>32367.93</v>
+        <v>37546.7988</v>
       </c>
       <c r="E43" t="n">
         <v>6.796292594215038</v>
@@ -2973,7 +2973,7 @@
         <v>375152.03</v>
       </c>
       <c r="D44" t="n">
-        <v>32856.59</v>
+        <v>38113.64439999999</v>
       </c>
       <c r="E44" t="n">
         <v>8.052915646733149</v>
@@ -2992,7 +2992,7 @@
         <v>355261.51</v>
       </c>
       <c r="D45" t="n">
-        <v>20738.5</v>
+        <v>24056.66</v>
       </c>
       <c r="E45" t="n">
         <v>5.515558363947916</v>
@@ -3011,7 +3011,7 @@
         <v>319416.87</v>
       </c>
       <c r="D46" t="n">
-        <v>51259.83</v>
+        <v>59461.4028</v>
       </c>
       <c r="E46" t="n">
         <v>13.82871650686434</v>
@@ -3030,7 +3030,7 @@
         <v>308113</v>
       </c>
       <c r="D47" t="n">
-        <v>13309.43</v>
+        <v>15438.9388</v>
       </c>
       <c r="E47" t="n">
         <v>4.140790672262667</v>
@@ -3049,7 +3049,7 @@
         <v>264423.75</v>
       </c>
       <c r="D48" t="n">
-        <v>40748.65</v>
+        <v>47268.434</v>
       </c>
       <c r="E48" t="n">
         <v>13.35266557526172</v>
@@ -3068,7 +3068,7 @@
         <v>240518</v>
       </c>
       <c r="D49" t="n">
-        <v>15516.47</v>
+        <v>17999.1052</v>
       </c>
       <c r="E49" t="n">
         <v>6.060305083139782</v>
@@ -3087,7 +3087,7 @@
         <v>201048.54</v>
       </c>
       <c r="D50" t="n">
-        <v>22335.05</v>
+        <v>25908.658</v>
       </c>
       <c r="E50" t="n">
         <v>9.998518691547575</v>
@@ -3106,7 +3106,7 @@
         <v>207681</v>
       </c>
       <c r="D51" t="n">
-        <v>14215.54</v>
+        <v>16490.0264</v>
       </c>
       <c r="E51" t="n">
         <v>6.4063820012696</v>
@@ -3125,7 +3125,7 @@
         <v>187357.23</v>
       </c>
       <c r="D52" t="n">
-        <v>16522.05</v>
+        <v>19165.578</v>
       </c>
       <c r="E52" t="n">
         <v>8.103839683954153</v>
@@ -3144,7 +3144,7 @@
         <v>193603.17</v>
       </c>
       <c r="D53" t="n">
-        <v>9586.469999999999</v>
+        <v>11120.3052</v>
       </c>
       <c r="E53" t="n">
         <v>4.717991527520792</v>
@@ -3163,7 +3163,7 @@
         <v>110175.15</v>
       </c>
       <c r="D54" t="n">
-        <v>50181.7</v>
+        <v>58210.77199999999</v>
       </c>
       <c r="E54" t="n">
         <v>31.29376761890745</v>
@@ -3182,7 +3182,7 @@
         <v>122673.59</v>
       </c>
       <c r="D55" t="n">
-        <v>27843.63</v>
+        <v>32298.6108</v>
       </c>
       <c r="E55" t="n">
         <v>18.49863424264679</v>
@@ -3201,7 +3201,7 @@
         <v>134655.4</v>
       </c>
       <c r="D56" t="n">
-        <v>8534.26</v>
+        <v>9899.741599999999</v>
       </c>
       <c r="E56" t="n">
         <v>5.960109130785002</v>
@@ -3220,7 +3220,7 @@
         <v>114157.92</v>
       </c>
       <c r="D57" t="n">
-        <v>12824.84</v>
+        <v>14876.8144</v>
       </c>
       <c r="E57" t="n">
         <v>10.09967022294995</v>
@@ -3239,7 +3239,7 @@
         <v>62281.44</v>
       </c>
       <c r="D58" t="n">
-        <v>12731.5</v>
+        <v>14768.54</v>
       </c>
       <c r="E58" t="n">
         <v>16.97240502771922</v>
@@ -3258,7 +3258,7 @@
         <v>59486.26</v>
       </c>
       <c r="D59" t="n">
-        <v>12957.72</v>
+        <v>15030.9552</v>
       </c>
       <c r="E59" t="n">
         <v>17.88653798424659</v>
@@ -3277,7 +3277,7 @@
         <v>56764.57</v>
       </c>
       <c r="D60" t="n">
-        <v>11696.65</v>
+        <v>13568.114</v>
       </c>
       <c r="E60" t="n">
         <v>17.08507385641097</v>
@@ -3296,7 +3296,7 @@
         <v>57294.57</v>
       </c>
       <c r="D61" t="n">
-        <v>4153.69</v>
+        <v>4818.2804</v>
       </c>
       <c r="E61" t="n">
         <v>6.759654382402365</v>
@@ -3315,7 +3315,7 @@
         <v>49954.82</v>
       </c>
       <c r="D62" t="n">
-        <v>7777.94</v>
+        <v>9022.410399999999</v>
       </c>
       <c r="E62" t="n">
         <v>13.4723162377825</v>
@@ -3334,7 +3334,7 @@
         <v>46721.5</v>
       </c>
       <c r="D63" t="n">
-        <v>5433.67</v>
+        <v>6303.057199999999</v>
       </c>
       <c r="E63" t="n">
         <v>10.41827684580455</v>
@@ -3353,7 +3353,7 @@
         <v>41513.96</v>
       </c>
       <c r="D64" t="n">
-        <v>4654.15</v>
+        <v>5398.813999999999</v>
       </c>
       <c r="E64" t="n">
         <v>10.08087617188574</v>
@@ -3372,7 +3372,7 @@
         <v>41939.8</v>
       </c>
       <c r="D65" t="n">
-        <v>1508.48</v>
+        <v>1749.8368</v>
       </c>
       <c r="E65" t="n">
         <v>3.471898082041452</v>
@@ -3391,7 +3391,7 @@
         <v>33416.8</v>
       </c>
       <c r="D66" t="n">
-        <v>3479.76</v>
+        <v>4036.5216</v>
       </c>
       <c r="E66" t="n">
         <v>9.43112311825276</v>
@@ -3410,7 +3410,7 @@
         <v>32159.08</v>
       </c>
       <c r="D67" t="n">
-        <v>3746.09</v>
+        <v>4345.4644</v>
       </c>
       <c r="E67" t="n">
         <v>10.43328857654761</v>
@@ -3429,7 +3429,7 @@
         <v>31591.74</v>
       </c>
       <c r="D68" t="n">
-        <v>2429.82</v>
+        <v>2818.5912</v>
       </c>
       <c r="E68" t="n">
         <v>7.142000543184969</v>
@@ -3448,7 +3448,7 @@
         <v>30129.41</v>
       </c>
       <c r="D69" t="n">
-        <v>1336.1</v>
+        <v>1549.876</v>
       </c>
       <c r="E69" t="n">
         <v>4.246236593654449</v>
@@ -3467,7 +3467,7 @@
         <v>15286.1</v>
       </c>
       <c r="D70" t="n">
-        <v>5050.11</v>
+        <v>5858.127599999999</v>
       </c>
       <c r="E70" t="n">
         <v>24.83309328532701</v>
@@ -3486,7 +3486,7 @@
         <v>14516.42</v>
       </c>
       <c r="D71" t="n">
-        <v>630.13</v>
+        <v>730.9508</v>
       </c>
       <c r="E71" t="n">
         <v>4.160221304521492</v>
@@ -3505,7 +3505,7 @@
         <v>6674.64</v>
       </c>
       <c r="D72" t="n">
-        <v>739.15</v>
+        <v>857.4139999999999</v>
       </c>
       <c r="E72" t="n">
         <v>9.969934406019053</v>
@@ -3524,7 +3524,7 @@
         <v>3894.83</v>
       </c>
       <c r="D73" t="n">
-        <v>948.26</v>
+        <v>1099.9816</v>
       </c>
       <c r="E73" t="n">
         <v>19.57964853017392</v>
@@ -3543,7 +3543,7 @@
         <v>1309.25</v>
       </c>
       <c r="D74" t="n">
-        <v>148.52</v>
+        <v>172.2832</v>
       </c>
       <c r="E74" t="n">
         <v>10.18816411368049</v>
@@ -3562,7 +3562,7 @@
         <v>599.14</v>
       </c>
       <c r="D75" t="n">
-        <v>21.55</v>
+        <v>24.998</v>
       </c>
       <c r="E75" t="n">
         <v>3.471942515587491</v>
@@ -3581,7 +3581,7 @@
         <v>362.11</v>
       </c>
       <c r="D76" t="n">
-        <v>198.23</v>
+        <v>229.9468</v>
       </c>
       <c r="E76" t="n">
         <v>35.37673555341399</v>
@@ -3600,7 +3600,7 @@
         <v>189.66</v>
       </c>
       <c r="D77" t="n">
-        <v>51.73</v>
+        <v>60.00679999999999</v>
       </c>
       <c r="E77" t="n">
         <v>21.43093876874637</v>
